--- a/artfynd/S 3051-2025 artfynd.xlsx
+++ b/artfynd/S 3051-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136015351</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
